--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>40.05</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90797.71114163064</v>
+        <v>138721.2863383297</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.729480212221536</v>
+        <v>2.642310215968185</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.05</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>138721.2863383297</v>
+        <v>139786.2546760342</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.642310215968185</v>
+        <v>2.662595327162556</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.14</v>
+        <v>41.63</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>139786.2546760342</v>
+        <v>157417.3971558075</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.662595327162556</v>
+        <v>2.998426612491571</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.63</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>157417.3971558075</v>
+        <v>150317.608237778</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.998426612491571</v>
+        <v>2.863192537862437</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.03</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>150317.608237778</v>
+        <v>174693.5501896792</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.863192537862437</v>
+        <v>3.327496194089128</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.09</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>174693.5501896792</v>
+        <v>201081.0990016889</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.327496194089128</v>
+        <v>3.830116171460742</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45.32</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>201081.0990016889</v>
+        <v>215517.3364683489</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.830116171460742</v>
+        <v>4.105092123206646</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46.54</v>
+        <v>45.76</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>215517.3364683489</v>
+        <v>206287.6108749106</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.105092123206646</v>
+        <v>3.929287826188773</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.763477484996</v>
+        <v>33.92810769595069</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.10905865219634</v>
+        <v>35.69082141459143</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.62378809486187</v>
+        <v>29.81510901912227</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>206287.6108749106</v>
+        <v>223619.132676979</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.929287826188773</v>
+        <v>4.259412050990075</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1745.564990527206</v>
+        <v>1412.972369208434</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>327.40912</v>
+        <v>342.141482</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100.840601</v>
+        <v>202.889509</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-565.814195</v>
+        <v>-512.40934</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-148.723541</v>
+        <v>-138.694069</v>
       </c>
     </row>
     <row r="7">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>1459.276975527206</v>
+        <v>1526.949027208434</v>
       </c>
     </row>
     <row r="10">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>34.10905865219634</v>
+        <v>35.69082141459143</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.10905865219634</v>
+        <v>35.69082141459143</v>
       </c>
     </row>
     <row r="13">
@@ -763,7 +763,7 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -812,13 +812,13 @@
         <v>62000</v>
       </c>
       <c r="D2" t="n">
-        <v>1.875058332599586</v>
+        <v>1.446751957877535</v>
       </c>
       <c r="E2" t="n">
-        <v>1.125034999559752</v>
+        <v>0.8680511747265207</v>
       </c>
       <c r="F2" t="n">
-        <v>1.096062422852328</v>
+        <v>0.8456965997527863</v>
       </c>
     </row>
     <row r="3">
@@ -834,13 +834,13 @@
         <v>55000</v>
       </c>
       <c r="D3" t="n">
-        <v>1.553165228238034</v>
+        <v>1.18338487249081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9318991369428203</v>
+        <v>0.710030923494486</v>
       </c>
       <c r="F3" t="n">
-        <v>0.884519517064131</v>
+        <v>0.6739315282663224</v>
       </c>
     </row>
     <row r="4">
@@ -856,13 +856,13 @@
         <v>48000</v>
       </c>
       <c r="D4" t="n">
-        <v>1.231272123876482</v>
+        <v>0.9200177871040854</v>
       </c>
       <c r="E4" t="n">
-        <v>0.738763274325889</v>
+        <v>0.5520106722624513</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6831452664098232</v>
+        <v>0.5104523882943416</v>
       </c>
     </row>
     <row r="5">
@@ -878,13 +878,13 @@
         <v>45000</v>
       </c>
       <c r="D5" t="n">
-        <v>1.093317936292959</v>
+        <v>0.8071461790812035</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6559907617757755</v>
+        <v>0.4842877074487221</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5909826682664644</v>
+        <v>0.4362952319357856</v>
       </c>
     </row>
     <row r="6">
@@ -900,13 +900,13 @@
         <v>43000</v>
       </c>
       <c r="D6" t="n">
-        <v>1.001348477903944</v>
+        <v>0.7318984403992821</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6008090867423665</v>
+        <v>0.4391390642395692</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5273303517598078</v>
+        <v>0.3854325147985407</v>
       </c>
     </row>
     <row r="7">
@@ -922,13 +922,13 @@
         <v>42000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9553637487094369</v>
+        <v>0.6942745710583215</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5732182492256621</v>
+        <v>0.4165647426349929</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4901573734808881</v>
+        <v>0.3562033839825093</v>
       </c>
     </row>
     <row r="8">
@@ -944,13 +944,13 @@
         <v>41000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9093790195149294</v>
+        <v>0.6566507017173608</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5456274117089576</v>
+        <v>0.3939904210304165</v>
       </c>
       <c r="F8" t="n">
-        <v>0.454549273304201</v>
+        <v>0.3282240879490841</v>
       </c>
     </row>
     <row r="9">
@@ -966,13 +966,13 @@
         <v>40000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8633942903204219</v>
+        <v>0.6190268323764002</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5180365741922531</v>
+        <v>0.3714160994258401</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4204501048553308</v>
+        <v>0.3014496383620162</v>
       </c>
     </row>
     <row r="10">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5.147196977992973</v>
+        <v>3.837685373341386</v>
       </c>
     </row>
     <row r="11">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>30.95477383412888</v>
+        <v>32.85282946097458</v>
       </c>
       <c r="F11" t="n">
-        <v>24.47659111686889</v>
+        <v>25.97742364578089</v>
       </c>
     </row>
     <row r="12">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29.62378809486187</v>
+        <v>29.81510901912227</v>
       </c>
     </row>
     <row r="13">
@@ -1036,7 +1036,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.11422645337098</v>
+        <v>26.9170547012132</v>
       </c>
       <c r="C2" t="n">
-        <v>27.77333922583964</v>
+        <v>29.87807077220972</v>
       </c>
       <c r="D2" t="n">
-        <v>31.43245199830832</v>
+        <v>32.83908684320622</v>
       </c>
       <c r="E2" t="n">
-        <v>35.09156477077699</v>
+        <v>35.80010291420274</v>
       </c>
       <c r="F2" t="n">
-        <v>38.75067754324565</v>
+        <v>38.76111898519925</v>
       </c>
     </row>
     <row r="3">
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.77973919671482</v>
+        <v>27.46156512758544</v>
       </c>
       <c r="C3" t="n">
-        <v>28.43885196918348</v>
+        <v>30.42258119858195</v>
       </c>
       <c r="D3" t="n">
-        <v>32.09796474165216</v>
+        <v>33.38359726957845</v>
       </c>
       <c r="E3" t="n">
-        <v>35.75707751412083</v>
+        <v>36.34461334057497</v>
       </c>
       <c r="F3" t="n">
-        <v>39.41619028658949</v>
+        <v>39.30562941157149</v>
       </c>
     </row>
     <row r="4">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.44525194005865</v>
+        <v>28.00607555395767</v>
       </c>
       <c r="C4" t="n">
-        <v>29.10436471252732</v>
+        <v>30.96709162495419</v>
       </c>
       <c r="D4" t="n">
-        <v>32.763477484996</v>
+        <v>33.92810769595069</v>
       </c>
       <c r="E4" t="n">
-        <v>36.42259025746467</v>
+        <v>36.88912376694721</v>
       </c>
       <c r="F4" t="n">
-        <v>40.08170302993333</v>
+        <v>39.85013983794372</v>
       </c>
     </row>
     <row r="5">
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.11076468340249</v>
+        <v>28.5505859803299</v>
       </c>
       <c r="C5" t="n">
-        <v>29.76987745587116</v>
+        <v>31.51160205132641</v>
       </c>
       <c r="D5" t="n">
-        <v>33.42899022833983</v>
+        <v>34.47261812232291</v>
       </c>
       <c r="E5" t="n">
-        <v>37.0881030008085</v>
+        <v>37.43363419331943</v>
       </c>
       <c r="F5" t="n">
-        <v>40.74721577327717</v>
+        <v>40.39465026431595</v>
       </c>
     </row>
     <row r="6">
@@ -1167,19 +1167,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.77627742674633</v>
+        <v>29.09509640670213</v>
       </c>
       <c r="C6" t="n">
-        <v>30.435390199215</v>
+        <v>32.05611247769865</v>
       </c>
       <c r="D6" t="n">
-        <v>34.09450297168367</v>
+        <v>35.01712854869515</v>
       </c>
       <c r="E6" t="n">
-        <v>37.75361574415235</v>
+        <v>37.97814461969167</v>
       </c>
       <c r="F6" t="n">
-        <v>41.41272851662101</v>
+        <v>40.93916069068818</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1217,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>32.83</v>
+        <v>33.98</v>
       </c>
     </row>
     <row r="3">
@@ -1225,7 +1225,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>32.88</v>
+        <v>34.01</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>32.89</v>
+        <v>34.03</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45.76</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>223619.132676979</v>
+        <v>208722.7237063726</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.259412050990075</v>
+        <v>3.975670927740431</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44.73</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>208722.7237063726</v>
+        <v>246903.8107766647</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.975670927740431</v>
+        <v>4.702929729079328</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.37</v>
+        <v>50.79</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>246903.8107766647</v>
+        <v>296365.6735722701</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.702929729079328</v>
+        <v>5.645060448995622</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/lpg_fv_report.xlsx
+++ b/outputs/lpg_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50.79</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>296365.6735722701</v>
+        <v>281758.5152612872</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.645060448995622</v>
+        <v>5.366828862119755</v>
       </c>
     </row>
   </sheetData>
